--- a/output/details/2026-05-20/preprocessed_data.xlsx
+++ b/output/details/2026-05-20/preprocessed_data.xlsx
@@ -15231,25 +15231,25 @@
         <v>46162</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1133411695748668</v>
+        <v>-0.1172767107445413</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1562639157963868</v>
+        <v>-0.1393889314134594</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1560485118421143</v>
+        <v>-0.1391152014812798</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1215491657696023</v>
+        <v>0.00310928243358365</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001699487105610955</v>
+        <v>0.001696430766842228</v>
       </c>
       <c r="G2" t="n">
-        <v>1.919044170551232</v>
+        <v>2.484077099942135</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4432316208070535</v>
+        <v>-0.2687668305933426</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
